--- a/results/supp_data/Supplementary Data 3.xlsx
+++ b/results/supp_data/Supplementary Data 3.xlsx
@@ -979,7 +979,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Number of weeks by which the laboratory signal precedes occupancy changes.</t>
+          <t>Number of weeks by which the occupancy signal precedes the laboratory series.</t>
         </is>
       </c>
     </row>
